--- a/xlsx/적용_보안설정_rocky8.xlsx
+++ b/xlsx/적용_보안설정_rocky8.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F46"/>
+  <dimension ref="B2:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -906,7 +906,8 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>최근 2개 패스워드 재사용 금지</t>
+          <t>최근 2개 패스워드 재사용 금지
+(authselect 적용 이후에 반영)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -990,12 +991,12 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>잠금 해제 시간</t>
+          <t>실패 카운트 유지 시간</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>600초 (10분) 경과 후 자동 해제</t>
+          <t>900초 (15분)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1005,18 +1006,18 @@
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="B25" s="9" t="n"/>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>실패 기록 표시 억제</t>
+          <t>잠금 해제 시간</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>silent 옵션 활성화</t>
+          <t>600초 (10분) 경과 후 자동 해제</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1026,43 +1027,43 @@
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>방화벽</t>
-        </is>
-      </c>
+      <c r="B26" s="9" t="n"/>
       <c r="C26" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>기본 존 설정</t>
+          <t>실패 기록 표시 억제</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>default zone = drop (미허용 트래픽 폐기)</t>
+          <t>silent 옵션 활성화</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>firewalld</t>
+          <t>/etc/security/faillock.conf</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="9" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>방화벽</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>SSH 포트 허용</t>
+          <t>기본 존 설정</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>24477/tcp 허용 (permanent)</t>
+          <t>default zone = drop (미허용 트래픽 폐기)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1072,43 +1073,43 @@
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>세션 및 명령 이력</t>
-        </is>
-      </c>
+      <c r="B28" s="9" t="n"/>
       <c r="C28" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>명령 이력 보관량</t>
+          <t>SSH 포트 허용</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>세션 10,000건 / 파일 20,000건</t>
+          <t>24477/tcp 허용 (permanent)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>/etc/profile.d/zzz-history.sh</t>
+          <t>firewalld</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="B29" s="8" t="n"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>세션 및 명령 이력</t>
+        </is>
+      </c>
       <c r="C29" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>명령 실행 시각 기록</t>
+          <t>명령 이력 보관량</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>이력에 날짜·시각 함께 저장 (YYYY-MM-DD HH:MM:SS)</t>
+          <t>세션 10,000건 / 파일 20,000건</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1118,64 +1119,64 @@
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
-      <c r="B30" s="9" t="n"/>
+      <c r="B30" s="8" t="n"/>
       <c r="C30" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>명령 즉시 기록</t>
+          <t>명령 실행 시각 기록</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>명령 실행 시점마다 이력 파일에 반영</t>
+          <t>이력에 날짜·시각 함께 저장 (YYYY-MM-DD HH:MM:SS)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>PROMPT_COMMAND</t>
+          <t>/etc/profile.d/zzz-history.sh</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>파일 권한</t>
-        </is>
-      </c>
+      <c r="B31" s="9" t="n"/>
       <c r="C31" s="5" t="n">
         <v>25</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>계정 정보 파일</t>
+          <t>명령 즉시 기록</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>/etc/passwd, /etc/group → 644 (root:root)</t>
+          <t>명령 실행 시점마다 이력 파일에 반영</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PROMPT_COMMAND</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
-      <c r="B32" s="8" t="n"/>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>파일 권한</t>
+        </is>
+      </c>
       <c r="C32" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>패스워드 파일</t>
+          <t>계정 정보 파일</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>/etc/shadow → 400 (root:root)</t>
+          <t>/etc/passwd, /etc/group → 644 (root:root)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1191,12 +1192,12 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>네트워크 설정 파일</t>
+          <t>패스워드 파일</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>/etc/hosts, /etc/services → 644</t>
+          <t>/etc/shadow → 400 (root:root)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -1212,12 +1213,12 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>프로파일</t>
+          <t>네트워크 설정 파일</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>/etc/profile → 755</t>
+          <t>/etc/hosts, /etc/services → 644</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -1233,12 +1234,12 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>계정 백업 파일</t>
+          <t>프로파일</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>passwd-, group-, shadow- → 600</t>
+          <t>/etc/profile → 755</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -1248,55 +1249,51 @@
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
-      <c r="B36" s="9" t="n"/>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="5" t="n">
         <v>30</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>신규 파일 기본 권한</t>
+          <t>계정 백업 파일</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>umask 027</t>
+          <t>passwd-, group-, shadow- → 600</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>/etc/profile.d/zzz-umask.sh</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>환경변수 / 콘솔</t>
-        </is>
-      </c>
+      <c r="B37" s="9" t="n"/>
       <c r="C37" s="5" t="n">
         <v>31</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>PATH 보호</t>
+          <t>신규 파일 기본 권한</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>PATH 에서 현재 디렉터리(.) 제거</t>
+          <t>umask 027</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>/etc/profile.d/zzz-path.sh</t>
+          <t>/etc/profile.d/zzz-umask.sh</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>세션 및 명령 이력</t>
+          <t>환경변수 / 콘솔</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -1304,24 +1301,24 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>유휴 세션 자동 종료</t>
+          <t>PATH 보호</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>1800초(30분) 무입력 시 로그아웃</t>
+          <t>PATH 에서 현재 디렉터리(.) 제거</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>/etc/profile</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
+          <t>/etc/profile.d/zzz-path.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="21" customHeight="1">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>환경변수 / 콘솔</t>
+          <t>세션 및 명령 이력</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -1329,95 +1326,99 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
+          <t>유휴 세션 자동 종료</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>1800초(30분) 무입력 시 로그아웃 (사용자 변경 불가)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>/etc/profile.d/zzz-timeout.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>환경변수 / 콘솔</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
           <t>root 콘솔 로그인 제한</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>pam_securetty 적용 및 원격 터미널(pts) 제외</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>허용 터미널을 물리 콘솔로 한정, 원격 터미널(pts) 제외
+(목록 파일이 없으면 표준 콘솔 목록을 생성한 뒤 적용)</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>/etc/pam.d/login
 /etc/securetty</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="10" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>스크립트 실행 후 수동 조치 사항</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>명령</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="B44" s="11" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>수동</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>SSH 포트 확인</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>ss -tlnp | grep sshd</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>방화벽은 24477 을 열지만 스크립트가 sshd 포트를 바꾸지는 않음.
 포트 변경이 필요하면 sshd_config 수정 + semanage port 등록 필요</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>수동</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>SELinux 포트 등록</t>
-        </is>
-      </c>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>semanage port -a -t ssh_port_t -p tcp 24477</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>SSH 포트를 변경하는 경우에만 필요</t>
-        </is>
-      </c>
-    </row>
     <row r="46" ht="22" customHeight="1">
       <c r="B46" s="11" t="inlineStr">
         <is>
@@ -1426,15 +1427,37 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
+          <t>SELinux 포트 등록</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>semanage port -a -t ssh_port_t -p tcp 24477</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>SSH 포트를 변경하는 경우에만 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>수동</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
           <t>접속 확인</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>새 터미널에서 SSH 재접속</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>현재 세션을 닫기 전에 반드시 확인</t>
         </is>
@@ -1442,13 +1465,13 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B32:B37"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B31:B36"/>
     <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B27:B28"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B15:B17"/>
   </mergeCells>

--- a/xlsx/적용_보안설정_rocky8.xlsx
+++ b/xlsx/적용_보안설정_rocky8.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F47"/>
+  <dimension ref="B2:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
-      <c r="B12" s="9" t="n"/>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="5" t="n">
         <v>6</v>
       </c>
@@ -736,156 +736,156 @@
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>계정 및 원격 접속</t>
-        </is>
-      </c>
+      <c r="B13" s="9" t="n"/>
       <c r="C13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>관리용 개인 계정 생성</t>
+          <t>표준시 설정</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>실행 중 입력받은 계정명 (패스워드도 함께 설정)</t>
+          <t>Asia/Seoul (KST, +0900)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>useradd / passwd</t>
+          <t>timedatectl</t>
         </is>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="9" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>계정 및 원격 접속</t>
+        </is>
+      </c>
       <c r="C14" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>root 원격 로그인 차단</t>
+          <t>관리용 개인 계정 생성</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>PermitRootLogin no</t>
+          <t>실행 중 입력받은 계정명 (패스워드도 함께 설정)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>/etc/ssh/sshd_config</t>
+          <t>useradd / passwd</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>관리자 권한</t>
-        </is>
-      </c>
+      <c r="B15" s="9" t="n"/>
       <c r="C15" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>su 명령 사용 제한</t>
+          <t>root 원격 로그인 차단</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>wheel 그룹 소속 계정만 su 사용 가능 (pam_wheel)</t>
+          <t>PermitRootLogin no</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>/etc/pam.d/su</t>
+          <t>/etc/ssh/sshd_config</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="B16" s="8" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>관리자 권한</t>
+        </is>
+      </c>
       <c r="C16" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>su 실행 파일 권한 제한</t>
+          <t>su 명령 사용 제한</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>4750 (root:wheel)</t>
+          <t>wheel 그룹 소속 계정만 su 사용 가능 (pam_wheel)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>/bin/su</t>
+          <t>/etc/pam.d/su</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
-      <c r="B17" s="9" t="n"/>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>관리 계정 sudo 권한 부여</t>
+          <t>su 실행 파일 권한 제한</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>생성 계정을 wheel 그룹에 추가</t>
+          <t>4750 (root:wheel)</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>usermod -aG wheel</t>
+          <t>/bin/su</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>패스워드 정책</t>
-        </is>
-      </c>
+      <c r="B18" s="9" t="n"/>
       <c r="C18" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>최소 길이</t>
+          <t>관리 계정 sudo 권한 부여</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>8자 이상</t>
+          <t>생성 계정을 wheel 그룹에 추가</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>/etc/security/pwquality.conf</t>
+          <t>usermod -aG wheel</t>
         </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
-      <c r="B19" s="8" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>패스워드 정책</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>복잡도</t>
+          <t>최소 길이</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>숫자·특수문자·대문자·소문자 각 1자 이상</t>
+          <t>8자 이상</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -894,72 +894,68 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="21" customHeight="1">
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="5" t="n">
         <v>14</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
+          <t>복잡도</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>숫자·특수문자·대문자·소문자 각 1자 이상</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>/etc/security/pwquality.conf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
           <t>재사용 제한</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>최근 2개 패스워드 재사용 금지
 (authselect 적용 이후에 반영)</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>/etc/pam.d/system-auth
 /etc/pam.d/password-auth</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>최대 사용 기간</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>90일</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>/etc/login.defs</t>
-        </is>
-      </c>
-    </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>계정 잠금</t>
-        </is>
-      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>잠금 기능 활성화</t>
+          <t>최대 사용 기간</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>authselect with-faillock 기능 활성화</t>
+          <t>90일</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>authselect</t>
+          <t>/etc/login.defs</t>
         </is>
       </c>
     </row>
@@ -970,75 +966,81 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>로그인 실패 잠금</t>
+          <t>최소 사용 기간</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>3회 연속 실패 시 계정 잠금</t>
+          <t>7일 (변경 후 7일간 재변경 불가)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>/etc/security/faillock.conf</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="21" customHeight="1">
-      <c r="B24" s="8" t="n"/>
+          <t>/etc/login.defs</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="9" t="n"/>
       <c r="C24" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>실패 카운트 유지 시간</t>
+          <t>기존 계정 일괄 적용</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>900초 (15분)</t>
+          <t>UID 1000 이상 계정에 90일/7일 정책 소급 적용
+※ 적용 시 즉시 만료되는 계정은 건너뛰고 목록만 안내
+  (서비스 계정 로그인 차단 방지)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>/etc/security/faillock.conf</t>
+          <t>chage</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>계정 잠금</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>잠금 해제 시간</t>
+          <t>잠금 기능 활성화</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>600초 (10분) 경과 후 자동 해제</t>
+          <t>authselect with-faillock 기능 활성화</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>/etc/security/faillock.conf</t>
+          <t>authselect</t>
         </is>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="B26" s="9" t="n"/>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="5" t="n">
         <v>20</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>실패 기록 표시 억제</t>
+          <t>로그인 실패 잠금</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>silent 옵션 활성화</t>
+          <t>3회 연속 실패 시 계정 잠금</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1048,94 +1050,90 @@
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>방화벽</t>
-        </is>
-      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="5" t="n">
         <v>21</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>기본 존 설정</t>
+          <t>실패 카운트 유지 시간</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>default zone = drop (미허용 트래픽 폐기)</t>
+          <t>900초 (15분)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>firewalld</t>
+          <t>/etc/security/faillock.conf</t>
         </is>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="9" t="n"/>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>SSH 포트 허용</t>
+          <t>잠금 해제 시간</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>24477/tcp 허용 (permanent)</t>
+          <t>600초 (10분) 경과 후 자동 해제</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>firewalld</t>
+          <t>/etc/security/faillock.conf</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>세션 및 명령 이력</t>
-        </is>
-      </c>
+      <c r="B29" s="9" t="n"/>
       <c r="C29" s="5" t="n">
         <v>23</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>명령 이력 보관량</t>
+          <t>실패 기록 표시 억제</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>세션 10,000건 / 파일 20,000건</t>
+          <t>silent 옵션 활성화</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>/etc/profile.d/zzz-history.sh</t>
+          <t>/etc/security/faillock.conf</t>
         </is>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
-      <c r="B30" s="8" t="n"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>방화벽</t>
+        </is>
+      </c>
       <c r="C30" s="5" t="n">
         <v>24</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>명령 실행 시각 기록</t>
+          <t>기본 존 설정</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>이력에 날짜·시각 함께 저장 (YYYY-MM-DD HH:MM:SS)</t>
+          <t>default zone = drop (미허용 트래픽 폐기)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>/etc/profile.d/zzz-history.sh</t>
+          <t>firewalld</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1144,24 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>명령 즉시 기록</t>
+          <t>SSH 포트 허용</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>명령 실행 시점마다 이력 파일에 반영</t>
+          <t>24477/tcp 허용 (permanent)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>PROMPT_COMMAND</t>
+          <t>firewalld</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>파일 권한</t>
+          <t>세션 및 명령 이력</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -1171,17 +1169,17 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>계정 정보 파일</t>
+          <t>명령 이력 보관량</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>/etc/passwd, /etc/group → 644 (root:root)</t>
+          <t>세션 10,000건 / 파일 20,000건</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/etc/profile.d/zzz-history.sh</t>
         </is>
       </c>
     </row>
@@ -1192,54 +1190,58 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>패스워드 파일</t>
+          <t>명령 실행 시각 기록</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>/etc/shadow → 400 (root:root)</t>
+          <t>이력에 날짜·시각 함께 저장 (YYYY-MM-DD HH:MM:SS)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/etc/profile.d/zzz-history.sh</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
-      <c r="B34" s="8" t="n"/>
+      <c r="B34" s="9" t="n"/>
       <c r="C34" s="5" t="n">
         <v>28</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>네트워크 설정 파일</t>
+          <t>명령 즉시 기록</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>/etc/hosts, /etc/services → 644</t>
+          <t>명령 실행 시점마다 이력 파일에 반영</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PROMPT_COMMAND</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
-      <c r="B35" s="8" t="n"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>파일 권한</t>
+        </is>
+      </c>
       <c r="C35" s="5" t="n">
         <v>29</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>프로파일</t>
+          <t>계정 정보 파일</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>/etc/profile → 755</t>
+          <t>/etc/passwd, /etc/group → 644 (root:root)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -1255,12 +1257,12 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>계정 백업 파일</t>
+          <t>패스워드 파일</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>passwd-, group-, shadow- → 600</t>
+          <t>/etc/shadow → 400 (root:root)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -1270,210 +1272,384 @@
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
-      <c r="B37" s="9" t="n"/>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="5" t="n">
         <v>31</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>신규 파일 기본 권한</t>
+          <t>네트워크 설정 파일</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>umask 027</t>
+          <t>/etc/hosts, /etc/services → 644</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>/etc/profile.d/zzz-umask.sh</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="21" customHeight="1">
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>환경변수 / 콘솔</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="5" t="n">
         <v>32</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>PATH 보호</t>
+          <t>프로파일 / PAM 설정</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>PATH 에서 현재 디렉터리(.) 제거</t>
+          <t>/etc/profile → 755
+system-auth, password-auth, su, login → 644</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>/etc/profile.d/zzz-path.sh</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>세션 및 명령 이력</t>
-        </is>
-      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="5" t="n">
         <v>33</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>유휴 세션 자동 종료</t>
+          <t>관리 명령어</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>1800초(30분) 무입력 시 로그아웃 (사용자 변경 불가)</t>
+          <t>last, ifconfig → 700 (root 전용 실행)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>/etc/profile.d/zzz-timeout.sh</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>환경변수 / 콘솔</t>
-        </is>
-      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="5" t="n">
         <v>34</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
+          <t>cron 접근 제어</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>cron.allow, cron.deny → 600
+※ cron.allow 생성 시 root + 기존 crontab 보유 계정을 포함
+  (빈 파일로 만들면 기존 사용자가 전부 차단됨)</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>접속 기록 파일</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>wtmp, btmp → 600
+(재부팅 후 원복 방지를 위해 tmpfiles 규칙으로 고정)</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>/etc/tmpfiles.d/zzz-wtmp.conf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>로그 파일</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>secure, messages → 600 (존재 시)
+journald 전용 환경에서는 해당 없음</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>계정 백업 파일</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>passwd-, group-, shadow- → 600</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>신규 파일 기본 권한</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>umask 027</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>/etc/profile.d/zzz-umask.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>환경변수 / 콘솔</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>PATH 보호</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>PATH 에서 현재 디렉터리(.) 제거</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>/etc/profile.d/zzz-path.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>세션 및 명령 이력</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>유휴 세션 자동 종료</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>1800초(30분) 무입력 시 로그아웃 (사용자 변경 불가)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>/etc/profile.d/zzz-timeout.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>환경변수 / 콘솔</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
           <t>root 콘솔 로그인 제한</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>허용 터미널을 물리 콘솔로 한정, 원격 터미널(pts) 제외
 (목록 파일이 없으면 표준 콘솔 목록을 생성한 뒤 적용)</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>/etc/pam.d/login
 /etc/securetty</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="10" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>스크립트 실행 후 수동 조치 사항</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="3" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>명령</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="B45" s="11" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>수동</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>SSH 포트 확인</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>ss -tlnp | grep sshd</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>방화벽은 24477 을 열지만 스크립트가 sshd 포트를 바꾸지는 않음.
 포트 변경이 필요하면 sshd_config 수정 + semanage port 등록 필요</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="11" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>수동</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>SELinux 포트 등록</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>semanage port -a -t ssh_port_t -p tcp 24477</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>SSH 포트를 변경하는 경우에만 필요</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="11" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>수동</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>접속 확인</t>
         </is>
       </c>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>새 터미널에서 SSH 재접속</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>현재 세션을 닫기 전에 반드시 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>수동</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>만료 계정 선조치</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>passwd &lt;계정&gt; &amp;&amp; chage -M 90 -m 7 &lt;계정&gt;</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>스크립트가 '즉시 만료됨'으로 건너뛴 계정이 있으면 수행</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B35:B44"/>
+    <mergeCell ref="B25:B29"/>
     <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B15:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
